--- a/Libraries/Vehicle/Steer/Rack/sm_car_data_Steer_Rack_WheelVarRatio.xlsx
+++ b/Libraries/Vehicle/Steer/Rack/sm_car_data_Steer_Rack_WheelVarRatio.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\Others\smiller\ssvt_srcR22a\Libraries\Vehicle\Steer\Rack\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16A6B757-00FF-4701-8A49-064A3687F900}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9631B40-384E-4202-88D0-114CA2BC6BC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1875" yWindow="600" windowWidth="26910" windowHeight="12765" xr2:uid="{68DBC447-E393-42D5-B761-B52508FAA163}"/>
+    <workbookView xWindow="6135" yWindow="2400" windowWidth="21600" windowHeight="11295" xr2:uid="{68DBC447-E393-42D5-B761-B52508FAA163}"/>
   </bookViews>
   <sheets>
     <sheet name="RWheelVarRatio_Hamba_f" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="36">
   <si>
     <t>Sedan</t>
   </si>
@@ -140,6 +140,12 @@
   </si>
   <si>
     <t>Cutoff frequency actuator</t>
+  </si>
+  <si>
+    <t>d</t>
+  </si>
+  <si>
+    <t>N/(m/s)</t>
   </si>
 </sst>
 </file>
@@ -259,13 +265,55 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{4E27A6AA-64BD-4439-9066-9FC6A29FF0A1}"/>
   </cellStyles>
-  <dxfs count="16">
+  <dxfs count="22">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -711,7 +759,7 @@
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="2" customWidth="1"/>
@@ -848,155 +896,180 @@
         <v>19.792000000000002</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="8"/>
-      <c r="B8" s="7" t="s">
+    <row r="8" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="19"/>
+      <c r="B8" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="20"/>
+      <c r="D8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" s="22"/>
+      <c r="G8" s="22"/>
+      <c r="H8" s="22">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="8"/>
+      <c r="B9" s="7" t="s">
         <v>11</v>
-      </c>
-      <c r="C8" s="7"/>
-      <c r="D8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>8</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F9" s="6">
-        <v>-1.0213531220517</v>
-      </c>
-      <c r="G9" s="6">
-        <v>0.37675517503754502</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
       <c r="H9" s="6">
-        <v>0.92326153885340301</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>7</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="8"/>
+      <c r="A10" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="B10" s="7" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
+        <v>4</v>
+      </c>
+      <c r="F10" s="6">
+        <v>-1.0213531220517</v>
+      </c>
+      <c r="G10" s="6">
+        <v>0.37675517503754502</v>
+      </c>
       <c r="H10" s="6">
-        <v>0.35289999999999999</v>
+        <v>0.92326153885340301</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="8"/>
       <c r="B11" s="7" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
       <c r="H11" s="6">
-        <v>1</v>
+        <v>0.35289999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="8"/>
       <c r="B12" s="7" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C12" s="7"/>
+      <c r="D12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="F12" s="6"/>
       <c r="G12" s="6"/>
-      <c r="H12" s="5" t="s">
+      <c r="H12" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="8"/>
+      <c r="B13" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="7"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="5" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="s">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="B13" s="20" t="s">
+      <c r="B14" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="C13" s="19"/>
-      <c r="D13" s="22" t="s">
+      <c r="C14" s="19"/>
+      <c r="D14" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E14" t="s">
         <v>30</v>
       </c>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21"/>
-      <c r="H13" s="21">
+      <c r="F14" s="21"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="21">
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="19"/>
-      <c r="B14" s="7" t="s">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="19"/>
+      <c r="B15" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="1" t="s">
+      <c r="C15" s="7"/>
+      <c r="D15" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="E15" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H14" s="1">
+      <c r="H15" s="1">
         <v>100</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B15" s="2"/>
-      <c r="H15" s="3"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B16" s="2"/>
       <c r="H16" s="3"/>
     </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B17" s="2"/>
+      <c r="H17" s="3"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A14:A16 B13:C13">
-    <cfRule type="cellIs" dxfId="15" priority="5" operator="equal">
-      <formula>"class"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A4:B12">
-    <cfRule type="cellIs" dxfId="14" priority="4" operator="equal">
-      <formula>"class"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E5 E7 E9:E12">
-    <cfRule type="cellIs" dxfId="13" priority="3" operator="equal">
-      <formula>"class"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E13">
-    <cfRule type="cellIs" dxfId="12" priority="1" operator="equal">
+  <conditionalFormatting sqref="A4:B7 A9:B13">
+    <cfRule type="cellIs" dxfId="21" priority="6" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B14:C14 A15:A17">
+    <cfRule type="cellIs" dxfId="20" priority="7" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E5 E7">
+    <cfRule type="cellIs" dxfId="19" priority="5" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E10:E14">
+    <cfRule type="cellIs" dxfId="18" priority="3" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A8:B8">
+    <cfRule type="cellIs" dxfId="17" priority="2" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E8">
+    <cfRule type="cellIs" dxfId="16" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1009,7 +1082,7 @@
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="2" customWidth="1"/>
@@ -1146,130 +1219,140 @@
         <v>19.792000000000002</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="8"/>
-      <c r="B8" s="7" t="s">
+    <row r="8" spans="1:10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="19"/>
+      <c r="B8" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="20"/>
+      <c r="D8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" s="22"/>
+      <c r="G8" s="22"/>
+      <c r="H8" s="22">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="8"/>
+      <c r="B9" s="7" t="s">
         <v>11</v>
-      </c>
-      <c r="C8" s="7"/>
-      <c r="D8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>8</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F9" s="4">
-        <v>-1.3243331220516996</v>
-      </c>
-      <c r="G9" s="4">
-        <v>0.45175517503754498</v>
-      </c>
-      <c r="H9" s="4">
-        <v>0.88921153885340298</v>
+        <v>10</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6">
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="8"/>
+      <c r="A10" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="B10" s="7" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6">
-        <v>0.35289999999999999</v>
+        <v>4</v>
+      </c>
+      <c r="F10" s="4">
+        <v>-1.3243331220516996</v>
+      </c>
+      <c r="G10" s="4">
+        <v>0.45175517503754498</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.88921153885340298</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="8"/>
       <c r="B11" s="7" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
       <c r="H11" s="6">
-        <v>1</v>
+        <v>0.35289999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="8"/>
       <c r="B12" s="7" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C12" s="7"/>
+      <c r="D12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="F12" s="6"/>
       <c r="G12" s="6"/>
-      <c r="H12" s="6" t="s">
+      <c r="H12" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="8"/>
+      <c r="B13" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="7"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="s">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="B13" s="20" t="s">
+      <c r="B14" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="C13" s="19"/>
-      <c r="D13" s="22" t="s">
+      <c r="C14" s="19"/>
+      <c r="D14" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E14" t="s">
         <v>30</v>
       </c>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21"/>
-      <c r="H13" s="21">
+      <c r="F14" s="21"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="21">
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="19"/>
-      <c r="B14" s="7" t="s">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="19"/>
+      <c r="B15" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="1" t="s">
+      <c r="C15" s="7"/>
+      <c r="D15" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="E15" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H14" s="1">
+      <c r="H15" s="1">
         <v>100</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F16" s="4"/>
@@ -1277,7 +1360,6 @@
       <c r="H16" s="4"/>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="2"/>
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
       <c r="H17" s="4"/>
@@ -1289,6 +1371,7 @@
       <c r="H18" s="4"/>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B19" s="2"/>
       <c r="F19" s="4"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
@@ -1299,41 +1382,56 @@
       <c r="H20" s="4"/>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B21" s="2"/>
-      <c r="H21" s="3"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="2"/>
       <c r="H22" s="3"/>
     </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="2"/>
+      <c r="H23" s="3"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A21:A22">
+  <conditionalFormatting sqref="A22:A23">
+    <cfRule type="cellIs" dxfId="15" priority="7" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A4:B7 A9:B13">
+    <cfRule type="cellIs" dxfId="14" priority="6" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A18:B21">
+    <cfRule type="cellIs" dxfId="13" priority="8" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B14:C14 A15">
+    <cfRule type="cellIs" dxfId="12" priority="4" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E5 E7">
     <cfRule type="cellIs" dxfId="11" priority="5" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A4:B12">
-    <cfRule type="cellIs" dxfId="10" priority="4" operator="equal">
-      <formula>"class"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A17:B20">
-    <cfRule type="cellIs" dxfId="9" priority="6" operator="equal">
-      <formula>"class"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E5 E7 E9:E12">
-    <cfRule type="cellIs" dxfId="8" priority="3" operator="equal">
-      <formula>"class"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A14 B13:C13">
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
-      <formula>"class"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E13">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+  <conditionalFormatting sqref="E10:E14">
+    <cfRule type="cellIs" dxfId="10" priority="3" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A8:B8">
+    <cfRule type="cellIs" dxfId="9" priority="2" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E8">
+    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1346,7 +1444,7 @@
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="2" customWidth="1"/>
@@ -1484,130 +1582,140 @@
         <v>19.792000000000002</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="8"/>
-      <c r="B8" s="7" t="s">
+    <row r="8" spans="1:10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="19"/>
+      <c r="B8" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="20"/>
+      <c r="D8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" s="22"/>
+      <c r="G8" s="22"/>
+      <c r="H8" s="22">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="8"/>
+      <c r="B9" s="7" t="s">
         <v>11</v>
-      </c>
-      <c r="C8" s="7"/>
-      <c r="D8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>8</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F9" s="18">
-        <v>-1.0213531220517</v>
-      </c>
-      <c r="G9" s="18">
-        <v>-0.37675517503754502</v>
-      </c>
-      <c r="H9" s="18">
-        <v>1.2232615388534001</v>
+        <v>10</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6">
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="8"/>
+      <c r="A10" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="B10" s="7" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6">
-        <v>0.35289999999999999</v>
+        <v>4</v>
+      </c>
+      <c r="F10" s="18">
+        <v>-1.0213531220517</v>
+      </c>
+      <c r="G10" s="18">
+        <v>-0.37675517503754502</v>
+      </c>
+      <c r="H10" s="18">
+        <v>1.2232615388534001</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="8"/>
       <c r="B11" s="7" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
       <c r="H11" s="6">
-        <v>1</v>
+        <v>0.35289999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="8"/>
       <c r="B12" s="7" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C12" s="7"/>
+      <c r="D12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="F12" s="6"/>
       <c r="G12" s="6"/>
-      <c r="H12" s="6" t="s">
+      <c r="H12" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="8"/>
+      <c r="B13" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="7"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="s">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="B13" s="20" t="s">
+      <c r="B14" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="C13" s="19"/>
-      <c r="D13" s="22" t="s">
+      <c r="C14" s="19"/>
+      <c r="D14" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E14" t="s">
         <v>30</v>
       </c>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21"/>
-      <c r="H13" s="21">
+      <c r="F14" s="21"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="21">
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="19"/>
-      <c r="B14" s="7" t="s">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="19"/>
+      <c r="B15" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="1" t="s">
+      <c r="C15" s="7"/>
+      <c r="D15" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="E15" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H14" s="1">
+      <c r="H15" s="1">
         <v>100</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F16" s="4"/>
@@ -1615,7 +1723,6 @@
       <c r="H16" s="4"/>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="2"/>
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
       <c r="H17" s="4"/>
@@ -1627,6 +1734,7 @@
       <c r="H18" s="4"/>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B19" s="2"/>
       <c r="F19" s="4"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
@@ -1637,40 +1745,55 @@
       <c r="H20" s="4"/>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B21" s="2"/>
-      <c r="H21" s="3"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="2"/>
       <c r="H22" s="3"/>
     </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="2"/>
+      <c r="H23" s="3"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A21:A22">
-    <cfRule type="cellIs" dxfId="7" priority="5" operator="equal">
-      <formula>"class"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A4:B12">
-    <cfRule type="cellIs" dxfId="6" priority="4" operator="equal">
-      <formula>"class"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A17:B20">
-    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
-      <formula>"class"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E5 E7 E9:E12">
-    <cfRule type="cellIs" dxfId="4" priority="3" operator="equal">
-      <formula>"class"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A14 B13:C13">
+  <conditionalFormatting sqref="A22:A23">
+    <cfRule type="cellIs" dxfId="7" priority="7" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A4:B7 A9:B13">
+    <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A18:B21">
+    <cfRule type="cellIs" dxfId="5" priority="8" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B14:C14 A15">
+    <cfRule type="cellIs" dxfId="4" priority="4" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E5 E7">
+    <cfRule type="cellIs" dxfId="3" priority="5" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E10:E14">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A8:B8">
     <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E13">
+  <conditionalFormatting sqref="E8">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
